--- a/docs/sample/成績資料_サンプル.xlsx
+++ b/docs/sample/成績資料_サンプル.xlsx
@@ -1022,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2510,85 +2510,182 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>レポート1 値が無い</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>停止</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>レポート2 値が無い</t>
+          <t>値が無い: レポート1、レポート2、発表、参加</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>停止</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>発表 値が無い</t>
-        </is>
-      </c>
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>【AI基礎】 20260050 佐藤 一郎（1A）  状態: 確定</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="14" t="n"/>
+      <c r="L48" s="14" t="n"/>
+      <c r="M48" s="14" t="n"/>
+      <c r="N48" s="14" t="n"/>
+      <c r="O48" s="14" t="n"/>
+      <c r="P48" s="14" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>停止</t>
-        </is>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>出席</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>20</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>参加 値が無い</t>
+          <t>出席回数</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>そのまま使用</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>14</v>
+      </c>
+      <c r="H49" t="n">
+        <v>15</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>AI基礎_出席.xlsx</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1学期</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>出席 小計</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>20</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>(14)÷(15)×20</t>
+        </is>
+      </c>
+      <c r="M50">
+        <f>SUM(G49:G49)/SUM(H49:H49)*B50</f>
+        <v/>
+      </c>
+      <c r="N50" t="n">
+        <v>18.66666666666667</v>
+      </c>
+      <c r="O50">
+        <f>IF(ABS(M50-N50)&lt;0.000000001,"一致","不一致")</f>
+        <v/>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>56/3（18.666666…）</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>【AI基礎】 20260050 佐藤 一郎（1A）  状態: 確定</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="n"/>
-      <c r="C51" s="14" t="n"/>
-      <c r="D51" s="14" t="n"/>
-      <c r="E51" s="14" t="n"/>
-      <c r="F51" s="14" t="n"/>
-      <c r="G51" s="14" t="n"/>
-      <c r="H51" s="14" t="n"/>
-      <c r="I51" s="14" t="n"/>
-      <c r="J51" s="14" t="n"/>
-      <c r="K51" s="14" t="n"/>
-      <c r="L51" s="14" t="n"/>
-      <c r="M51" s="14" t="n"/>
-      <c r="N51" s="14" t="n"/>
-      <c r="O51" s="14" t="n"/>
-      <c r="P51" s="14" t="n"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>課題</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>40</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>課題1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>そのまま使用</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>AI基礎_課題一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>課題</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>H33</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>出席</t>
+          <t>課題</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>出席回数</t>
+          <t>課題2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2602,113 +2699,113 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AI基礎_出席.xlsx</t>
+          <t>AI基礎_課題一覧.xlsx</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>1学期</t>
+          <t>課題</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>G14</t>
+          <t>I33</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>出席 小計</t>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>課題</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>20</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>(14)÷(15)×20</t>
-        </is>
-      </c>
-      <c r="M53">
-        <f>SUM(G52:G52)/SUM(H52:H52)*B53</f>
-        <v/>
-      </c>
-      <c r="N53" t="n">
-        <v>18.66666666666667</v>
-      </c>
-      <c r="O53">
-        <f>IF(ABS(M53-N53)&lt;0.000000001,"一致","不一致")</f>
-        <v/>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>56/3（18.666666…）</t>
+        <v>40</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>課題3</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>そのまま使用</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>AI基礎_課題一覧.xlsx</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>課題</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>J33</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>課題</t>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>課題 小計</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>40</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>課題1</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>そのまま使用</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>6</v>
-      </c>
-      <c r="H54" t="n">
-        <v>10</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>AI基礎_課題一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>課題</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>H33</t>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>(6+7+8)÷(10+10+10)×40</t>
+        </is>
+      </c>
+      <c r="M54">
+        <f>SUM(G51:G53)/SUM(H51:H53)*B54</f>
+        <v/>
+      </c>
+      <c r="N54" t="n">
+        <v>28</v>
+      </c>
+      <c r="O54">
+        <f>IF(ABS(M54-N54)&lt;0.000000001,"一致","不一致")</f>
+        <v/>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>課題</t>
+          <t>試験</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2716,12 +2813,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>課題2</t>
+          <t>期末試験</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2735,98 +2832,75 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="H55" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AI基礎_課題一覧.xlsx</t>
+          <t>AI基礎_試験.xlsx</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>課題</t>
+          <t>期末</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>I33</t>
+          <t>C16</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>課題</t>
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>試験 小計</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>40</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>課題3</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>そのまま使用</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>8</v>
-      </c>
-      <c r="H56" t="n">
-        <v>10</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>AI基礎_課題一覧.xlsx</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>課題</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>J33</t>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>(62)÷(100)×40</t>
+        </is>
+      </c>
+      <c r="M56">
+        <f>SUM(G55:G55)/SUM(H55:H55)*B56</f>
+        <v/>
+      </c>
+      <c r="N56" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O56">
+        <f>IF(ABS(M56-N56)&lt;0.000000001,"一致","不一致")</f>
+        <v/>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>24.8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>課題 小計</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>40</v>
+          <t>合計</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>(6+7+8)÷(10+10+10)×40</t>
+          <t>56/3 + 28 + 24.8</t>
         </is>
       </c>
       <c r="M57">
-        <f>SUM(G54:G56)/SUM(H54:H56)*B57</f>
+        <f>M50+M54+M56</f>
         <v/>
       </c>
       <c r="N57" t="n">
-        <v>28</v>
+        <v>71.46666666666667</v>
       </c>
       <c r="O57">
         <f>IF(ABS(M57-N57)&lt;0.000000001,"一致","不一致")</f>
@@ -2834,184 +2908,201 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1072/15（71.466666…）</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>試験</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>40</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>期末試験</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>A: 90以上 / B: 80以上 / C: 70以上 / D: 60以上 / E: 0以上</t>
+        </is>
+      </c>
+      <c r="M58">
+        <f>IF(M57&gt;=90,"A",IF(M57&gt;=80,"B",IF(M57&gt;=70,"C",IF(M57&gt;=60,"D",IF(M57&gt;=0,"E","")))))</f>
+        <v/>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O58">
+        <f>IF(M58=N58,"一致","不一致")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>【マーケティング】 20260050 佐藤 一郎（1A）  状態: 確定</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="n"/>
+      <c r="C60" s="14" t="n"/>
+      <c r="D60" s="14" t="n"/>
+      <c r="E60" s="14" t="n"/>
+      <c r="F60" s="14" t="n"/>
+      <c r="G60" s="14" t="n"/>
+      <c r="H60" s="14" t="n"/>
+      <c r="I60" s="14" t="n"/>
+      <c r="J60" s="14" t="n"/>
+      <c r="K60" s="14" t="n"/>
+      <c r="L60" s="14" t="n"/>
+      <c r="M60" s="14" t="n"/>
+      <c r="N60" s="14" t="n"/>
+      <c r="O60" s="14" t="n"/>
+      <c r="P60" s="14" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>課題</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>50</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>レポート1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>数値</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>そのまま使用</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>62</v>
-      </c>
-      <c r="H58" t="n">
-        <v>100</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>AI基礎_試験.xlsx</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>期末</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>試験 小計</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>40</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>(62)÷(100)×40</t>
-        </is>
-      </c>
-      <c r="M59">
-        <f>SUM(G58:G58)/SUM(H58:H58)*B59</f>
+      <c r="G61" t="n">
+        <v>12</v>
+      </c>
+      <c r="H61" t="n">
+        <v>20</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>マーケ_評価表.xlsx</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>成績</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>課題</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>50</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>レポート2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>対象外 → 計算から除外（採点ルールによる）</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>マーケ_評価表.xlsx</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>成績</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>課題 小計</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>50</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>(12)÷(20)×50</t>
+        </is>
+      </c>
+      <c r="M63">
+        <f>SUM(G61:G62)/SUM(H61:H62)*B63</f>
         <v/>
       </c>
-      <c r="N59" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O59">
-        <f>IF(ABS(M59-N59)&lt;0.000000001,"一致","不一致")</f>
+      <c r="N63" t="n">
+        <v>30</v>
+      </c>
+      <c r="O63">
+        <f>IF(ABS(M63-N63)&lt;0.000000001,"一致","不一致")</f>
         <v/>
       </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>56/3 + 28 + 24.8</t>
-        </is>
-      </c>
-      <c r="M60">
-        <f>M53+M57+M59</f>
-        <v/>
-      </c>
-      <c r="N60" t="n">
-        <v>71.46666666666667</v>
-      </c>
-      <c r="O60">
-        <f>IF(ABS(M60-N60)&lt;0.000000001,"一致","不一致")</f>
-        <v/>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>1072/15（71.466666…）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>評価</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>A: 90以上 / B: 80以上 / C: 70以上 / D: 60以上 / E: 0以上</t>
-        </is>
-      </c>
-      <c r="M61">
-        <f>IF(M60&gt;=90,"A",IF(M60&gt;=80,"B",IF(M60&gt;=70,"C",IF(M60&gt;=60,"D",IF(M60&gt;=0,"E","")))))</f>
-        <v/>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O61">
-        <f>IF(M61=N61,"一致","不一致")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>【マーケティング】 20260050 佐藤 一郎（1A）  状態: 確定</t>
-        </is>
-      </c>
-      <c r="B63" s="14" t="n"/>
-      <c r="C63" s="14" t="n"/>
-      <c r="D63" s="14" t="n"/>
-      <c r="E63" s="14" t="n"/>
-      <c r="F63" s="14" t="n"/>
-      <c r="G63" s="14" t="n"/>
-      <c r="H63" s="14" t="n"/>
-      <c r="I63" s="14" t="n"/>
-      <c r="J63" s="14" t="n"/>
-      <c r="K63" s="14" t="n"/>
-      <c r="L63" s="14" t="n"/>
-      <c r="M63" s="14" t="n"/>
-      <c r="N63" s="14" t="n"/>
-      <c r="O63" s="14" t="n"/>
-      <c r="P63" s="14" t="n"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>課題</t>
+          <t>発表</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>レポート1</t>
+          <t>発表</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3025,174 +3116,157 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H64" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>マーケ_評価表.xlsx</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>成績</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>発表 小計</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>30</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>(20)÷(30)×30</t>
+        </is>
+      </c>
+      <c r="M65">
+        <f>SUM(G64:G64)/SUM(H64:H64)*B65</f>
+        <v/>
+      </c>
+      <c r="N65" t="n">
         <v>20</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="O65">
+        <f>IF(ABS(M65-N65)&lt;0.000000001,"一致","不一致")</f>
+        <v/>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>参加</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>20</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>参加</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>数値</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>そのまま使用</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>7</v>
+      </c>
+      <c r="H66" t="n">
+        <v>10</v>
+      </c>
+      <c r="I66" t="inlineStr">
         <is>
           <t>マーケ_評価表.xlsx</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>成績</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>D7</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>課題</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>50</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>レポート2</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>対象外</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>対象外 → 計算から除外（採点ルールによる）</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>マーケ_評価表.xlsx</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>成績</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>E7</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>課題 小計</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>50</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>(12)÷(20)×50</t>
-        </is>
-      </c>
-      <c r="M66">
-        <f>SUM(G64:G65)/SUM(H64:H65)*B66</f>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>参加 小計</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>20</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>(7)÷(10)×20</t>
+        </is>
+      </c>
+      <c r="M67">
+        <f>SUM(G66:G66)/SUM(H66:H66)*B67</f>
         <v/>
       </c>
-      <c r="N66" t="n">
-        <v>30</v>
-      </c>
-      <c r="O66">
-        <f>IF(ABS(M66-N66)&lt;0.000000001,"一致","不一致")</f>
+      <c r="N67" t="n">
+        <v>14</v>
+      </c>
+      <c r="O67">
+        <f>IF(ABS(M67-N67)&lt;0.000000001,"一致","不一致")</f>
         <v/>
       </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>発表</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>30</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>発表</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>そのまま使用</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>20</v>
-      </c>
-      <c r="H67" t="n">
-        <v>30</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>マーケ_評価表.xlsx</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>成績</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>F7</t>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>発表 小計</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>30</v>
+          <t>合計</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>(20)÷(30)×30</t>
+          <t>30 + 20 + 14</t>
         </is>
       </c>
       <c r="M68">
-        <f>SUM(G67:G67)/SUM(H67:H67)*B68</f>
+        <f>M63+M65+M67</f>
         <v/>
       </c>
       <c r="N68" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="O68">
         <f>IF(ABS(M68-N68)&lt;0.000000001,"一致","不一致")</f>
@@ -3200,142 +3274,32 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>参加</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>20</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>参加</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>数値</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>そのまま使用</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>7</v>
-      </c>
-      <c r="H69" t="n">
-        <v>10</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>マーケ_評価表.xlsx</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>成績</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>G7</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>参加 小計</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>20</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>(7)÷(10)×20</t>
-        </is>
-      </c>
-      <c r="M70">
-        <f>SUM(G69:G69)/SUM(H69:H69)*B70</f>
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>A: 90以上 / B: 80以上 / C: 70以上 / D: 60以上 / E: 0以上</t>
+        </is>
+      </c>
+      <c r="M69">
+        <f>IF(M68&gt;=90,"A",IF(M68&gt;=80,"B",IF(M68&gt;=70,"C",IF(M68&gt;=60,"D",IF(M68&gt;=0,"E","")))))</f>
         <v/>
       </c>
-      <c r="N70" t="n">
-        <v>14</v>
-      </c>
-      <c r="O70">
-        <f>IF(ABS(M70-N70)&lt;0.000000001,"一致","不一致")</f>
-        <v/>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>30 + 20 + 14</t>
-        </is>
-      </c>
-      <c r="M71">
-        <f>M66+M68+M70</f>
-        <v/>
-      </c>
-      <c r="N71" t="n">
-        <v>64</v>
-      </c>
-      <c r="O71">
-        <f>IF(ABS(M71-N71)&lt;0.000000001,"一致","不一致")</f>
-        <v/>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>評価</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>A: 90以上 / B: 80以上 / C: 70以上 / D: 60以上 / E: 0以上</t>
-        </is>
-      </c>
-      <c r="M72">
-        <f>IF(M71&gt;=90,"A",IF(M71&gt;=80,"B",IF(M71&gt;=70,"C",IF(M71&gt;=60,"D",IF(M71&gt;=0,"E","")))))</f>
-        <v/>
-      </c>
-      <c r="N72" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="O72">
-        <f>IF(M72=N72,"一致","不一致")</f>
+      <c r="O69">
+        <f>IF(M69=N69,"一致","不一致")</f>
         <v/>
       </c>
     </row>
@@ -4857,7 +4821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4981,14 +4945,14 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>レポート1 値が無い</t>
+          <t>値が無い: レポート1、レポート2、発表、参加</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>停止</t>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -5003,24 +4967,24 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>マーケティング</t>
+          <t>AI基礎</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>レポート2 値が無い</t>
+          <t>資料「AI基礎_出席.xlsx」の13行目: 氏名の表記（空白・全角半角・ローマ字）のみ異なる</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>停止</t>
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>20260082</t>
+          <t>20260031</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5030,91 +4994,10 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>マーケティング</t>
+          <t>AI基礎</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>発表 値が無い</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>停止</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>20260082</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>山田 花子</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>マーケティング</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>参加 値が無い</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>20260082</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>山田 花子</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>AI基礎</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>資料「AI基礎_出席.xlsx」の13行目: 氏名の表記（空白・全角半角・ローマ字）のみ異なる</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>20260031</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>山田 花子</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>AI基礎</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>合計に端数がある（89.6）。端数の扱いで評価が B から A に変わり得る</t>
         </is>
